--- a/dados/csv/inspecoes.xlsx
+++ b/dados/csv/inspecoes.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,76 +425,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>op</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>codigo</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>descricao</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>quantidade</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>data_hora_inicio_inspecao</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>data_hora_fim_inspecao</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>possui_op</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>qtd_etiquetas</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>conformidade</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>refugo</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>aprovado</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>observacao</t>
         </is>
@@ -516,12 +523,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-12T16:48:00</t>
+          <t>12/07/2026 16:48:00</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-12T16:49:00</t>
+          <t>12/07/2026 16:49:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -531,30 +538,25 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Conforme</t>
+          <t>True</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
         <is>
           <t>Item sem op</t>
         </is>
@@ -588,12 +590,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-14T14:36:00</t>
+          <t>14/07/2026 14:36:00</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-14T14:43:00</t>
+          <t>14/07/2026 14:43:00</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -603,30 +605,25 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>Não conforme</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Não conforme</t>
+          <t>True</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
         <is>
           <t>Nao foi trocado a caixa de kit</t>
         </is>
@@ -660,12 +657,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-14T15:40:00</t>
+          <t>14/07/2026 15:40:00</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-14T15:53:00</t>
+          <t>14/07/2026 15:53:00</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -675,30 +672,25 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>Não conforme</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Não conforme</t>
+          <t>True</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
         <is>
           <t>Motor faltando parafuso</t>
         </is>
@@ -732,12 +724,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-14T16:00:00</t>
+          <t>14/07/2026 16:00:00</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-14T16:02:00</t>
+          <t>14/07/2026 16:02:00</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -747,30 +739,25 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Conforme</t>
+          <t>True</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
         <is>
           <t>Capacitor de 30</t>
         </is>
@@ -804,12 +791,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-14T16:05:00</t>
+          <t>14/07/2026 16:05:00</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-14T16:12:00</t>
+          <t>14/07/2026 16:12:00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -819,32 +806,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>Não conforme</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Não conforme</t>
+          <t>True</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Motores sujos de PU e óleo 
+          <t>Motores sujos de PU e óleo 
 Etiqueta pivo na central pivo dupla</t>
         </is>
       </c>

--- a/dados/csv/inspecoes.xlsx
+++ b/dados/csv/inspecoes.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,411 +413,1564 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>op</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>codigo</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>descricao</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>quantidade</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>data_hora_inicio_inspecao</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>data_hora_fim_inspecao</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>possui_op</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>conformidade</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>refugo</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>aprovado</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>observacao</t>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>observacao geral</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>item conferido</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>codigo nc</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>observacao_refugo</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>97159</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>97159</t>
+          <t>2001161</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2001161</t>
+          <t>CONJ. MOVIMENTADOR TRINO 300 220V LIGHT 50-60HZ SEM CREMALHEIRA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CONJ. MOVIMENTADOR TRINO 300 220V LIGHT 50-60HZ SEM CREMALHEIRA</t>
+          <t>200</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>12/07/2026 16:48:00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>12/07/2026 16:48:00</t>
+          <t>12/07/2026 16:49:00</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>12/07/2026 16:49:00</t>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Conforme</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
           <t>Item sem op</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>97634</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>97634</t>
+          <t>2007089</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2007089</t>
+          <t>CONJUNTO MOVIMENTADOR TRINO PIVÔ 3 220V SEM ACIONAMENTO - DUPLO</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CONJUNTO MOVIMENTADOR TRINO PIVÔ 3 220V SEM ACIONAMENTO - DUPLO</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>14/07/2026 14:36:00</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>14/07/2026 14:36:00</t>
+          <t>14/07/2026 14:43:00</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>14/07/2026 14:43:00</t>
+          <t>Não conforme</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
           <t>Nao foi trocado a caixa de kit</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>95437</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>95437</t>
+          <t>2008004</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2008004</t>
+          <t>CONJ. MOVIMENTADOR TRINO BV4 220V SEM ACIONAMENTO</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CONJ. MOVIMENTADOR TRINO BV4 220V SEM ACIONAMENTO</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>14/07/2026 15:40:00</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>14/07/2026 15:40:00</t>
+          <t>14/07/2026 15:53:00</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>14/07/2026 15:53:00</t>
+          <t>Não conforme</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
           <t>Motor faltando parafuso</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>96959</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>96959</t>
+          <t>2007087</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2007087</t>
+          <t>CONJUNTO MOVIMENTADOR TRINO PIVÔ 3 127V SEM ACIONAMENTO - DUPLO</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CONJUNTO MOVIMENTADOR TRINO PIVÔ 3 127V SEM ACIONAMENTO - DUPLO</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>14/07/2026 16:00:00</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>14/07/2026 16:00:00</t>
+          <t>14/07/2026 16:02:00</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>14/07/2026 16:02:00</t>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Conforme</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
           <t>Capacitor de 30</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>97319</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>2007087</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CONJUNTO MOVIMENTADOR TRINO PIVÔ 3 127V SEM ACIONAMENTO - DUPLO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>14/07/2026 16:05:00</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>14/07/2026 16:12:00</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Motores sujos de PU e óleo 
+Etiqueta pivo na central pivo dupla</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>97319</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>2007087</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>CONJUNTO MOVIMENTADOR TRINO PIVÔ 3 127V SEM ACIONAMENTO - DUPLO</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>14/07/2026 16:05:00</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>14/07/2026 16:12:00</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>16/07/2026 15:20:00</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>16/07/2026 15:22:00</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>Não conforme</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Motores sujos de PU e óleo 
-Etiqueta pivo na central pivo dupla</t>
-        </is>
-      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Motores sujos de PU
+Motor com 3 manuais 
+Motor com etiquetas de pivô simples na central dupla</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>96959</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2007087</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CONJUNTO MOVIMENTADOR TRINO PIVÔ 3 127V SEM ACIONAMENTO - DUPLO</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>16/07/2026 15:23:00</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>16/07/2026 15:24:00</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Parafuso do mancal solto 
+Central 220v na linha de produção 127v</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>97634</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2007089</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CONJUNTO MOVIMENTADOR TRINO PIVÔ 3 220V SEM ACIONAMENTO - DUPLO</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>16/07/2026 15:25:00</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>16/07/2026 15:25:00</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Conforme</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>97779</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2008002</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CONJ. MOVIMENTADOR TRINO BV3 220V SEM ACIONAMENTO</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>23/07/2026 07:35:00</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>23/07/2026 07:36:00</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Conforme</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>98567</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2006041</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CONJ. MOVIMENTADOR INTELIGENTE - IZZY 300 220V 50-60HZ SEM CREMALHEIRA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>29/07/2026 08:33:00</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>29/07/2026 08:37:00</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Conforme</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>97600</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2006041</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CONJ. MOVIMENTADOR INTELIGENTE - IZZY 300 220V 50-60HZ SEM CREMALHEIRA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>29/07/2026 08:43:00</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>29/07/2026 08:46:00</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Conforme</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>97600</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2006041</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CONJ. MOVIMENTADOR INTELIGENTE - IZZY 300 220V 50-60HZ SEM CREMALHEIRA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>29/07/2026 08:43:00</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>29/07/2026 08:46:00</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Conforme</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>95317</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2006151</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Inteligente - Izzy 500 127V 50-60Hz C/Cremalheira Door Line EX</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>29/07/2026 08:47:00</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>29/07/2026 08:49:00</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Conforme</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>98571</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2001161</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CONJ. MOVIMENTADOR TRINO 300 220V LIGHT 50-60HZ SEM CREMALHEIRA</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>29/07/2026 08:49:00</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>29/07/2026 08:53:00</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Conforme</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>98420</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2007089</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CONJUNTO MOVIMENTADOR TRINO PIVÔ 3 220V SEM ACIONAMENTO - DUPLO</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>29/07/2026 08:56:00</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>29/07/2026 08:58:00</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Conforme</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>98154</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2007089</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CONJUNTO MOVIMENTADOR TRINO PIVÔ 3 220V SEM ACIONAMENTO - DUPLO</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>29/07/2026 08:58:00</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>29/07/2026 09:14:00</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Conforme</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kit flex na linha montando pivo duplo</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>98270</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2007089</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CONJUNTO MOVIMENTADOR TRINO PIVÔ 3 220V SEM ACIONAMENTO - DUPLO</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>29/07/2026 09:15:00</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>29/07/2026 09:16:00</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Motores sujos de PU</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>98549</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2008002</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CONJ. MOVIMENTADOR TRINO BV3 220V SEM ACIONAMENTO</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>29/07/2026 09:17:00</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>29/07/2026 09:18:00</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Conforme</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>99102</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2006041</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CONJ. MOVIMENTADOR INTELIGENTE - IZZY 300 220V 50-60HZ SEM CREMALHEIRA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>03/08/2026 11:46:00</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>03/08/2026 11:48:00</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Estator</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>99102</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2006041</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CONJ. MOVIMENTADOR INTELIGENTE - IZZY 300 220V 50-60HZ SEM CREMALHEIRA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>03/08/2026 11:46:00</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>03/08/2026 11:48:00</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Capacitor</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>98736</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2008002</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CONJ. MOVIMENTADOR TRINO BV3 220V SEM ACIONAMENTO</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>03/08/2026 13:14:00</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>03/08/2026 13:19:00</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>INDUZIDO: Sem iduzido ate o momento da inspeção</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>98587</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2007089</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CONJUNTO MOVIMENTADOR TRINO PIVÔ 3 220V SEM ACIONAMENTO - DUPLO</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>03/08/2026 13:23:00</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>03/08/2026 13:37:00</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>ETIQUETA INTERNA : Com op destinada a outro produto 
+KIT : Sem kit ate o momento da inspeção</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>98421</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2007089</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CONJUNTO MOVIMENTADOR TRINO PIVÔ 3 220V SEM ACIONAMENTO - DUPLO</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>03/08/2026 13:39:00</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>03/08/2026 13:48:00</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Sem kit para coNF
+PARAFUSO DA CARCAÇA : Faltando um parafuso
+LIMPEZA: sujo de PU</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>98783</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2001161</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CONJ. MOVIMENTADOR TRINO 300 220V LIGHT 50-60HZ SEM CREMALHEIRA</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>03/08/2026 13:55:00</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>03/08/2026 14:00:00</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>97950</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2001042</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CONJ. MOVIMENTADOR TRINO 900 220V 50-60HZ SEM CREMALHEIRA</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>03/08/2026 14:02:00</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>03/08/2026 14:17:00</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Engrenagem montada errado</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>99102</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2006041</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CONJ. MOVIMENTADOR INTELIGENTE - IZZY 300 220V 50-60HZ SEM CREMALHEIRA</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>03/08/2026 14:21:00</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>03/08/2026 14:25:00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>98734</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2006041</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CONJ. MOVIMENTADOR INTELIGENTE - IZZY 300 220V 50-60HZ SEM CREMALHEIRA</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>03/08/2026 14:30:00</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>03/08/2026 14:31:00</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>97427</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2008004</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CONJ. MOVIMENTADOR TRINO BV4 220V SEM ACIONAMENTO</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>04/08/2026 07:05:00</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>04/08/2026 07:08:00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>98587</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2007089</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CONJUNTO MOVIMENTADOR TRINO PIVÔ 3 220V SEM ACIONAMENTO - DUPLO</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>04/08/2026 07:20:00</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>04/08/2026 07:31:00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Carcaça</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Carcaças trincadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>98421</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2007089</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CONJUNTO MOVIMENTADOR TRINO PIVÔ 3 220V SEM ACIONAMENTO - DUPLO</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>04/08/2026 07:36:00</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>04/08/2026 07:44:00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Carcaça</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Carcaças trincadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>98421</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2007089</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CONJUNTO MOVIMENTADOR TRINO PIVÔ 3 220V SEM ACIONAMENTO - DUPLO</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>04/08/2026 07:36:00</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>04/08/2026 07:44:00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Limpeza</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Motores sujos de PU</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>95317</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2006151</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CONJ. MOVIMENTADOR INTELIGENTE - IZZY 500 127V 50-60HZ C/ CREMALHEIRA 3MT DOOR LINE AUTOMATIC EX</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>04/08/2026 08:16:00</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>04/08/2026 08:20:00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Pedido não tem etiqueta externa</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>99102</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2006041</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CONJ. MOVIMENTADOR INTELIGENTE - IZZY 300 220V 50-60HZ SEM CREMALHEIRA</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>04/08/2026 08:25:00</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>04/08/2026 08:28:00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>98981</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2006041</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CONJ. MOVIMENTADOR INTELIGENTE - IZZY 300 220V 50-60HZ SEM CREMALHEIRA</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>04/08/2026 08:39:00</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>04/08/2026 08:40:00</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>98734</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2006041</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CONJ. MOVIMENTADOR INTELIGENTE - IZZY 300 220V 50-60HZ SEM CREMALHEIRA</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>04/08/2026 08:42:00</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>04/08/2026 08:45:00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>98736</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2008002</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CONJ. MOVIMENTADOR TRINO BV3 220V SEM ACIONAMENTO</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>04/08/2026 09:36:00</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>04/08/2026 09:38:00</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dados/csv/inspecoes.xlsx
+++ b/dados/csv/inspecoes.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,63 +425,73 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>op</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>codigo</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>descricao</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>secao</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>quantidade</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>data_hora_inicio_inspecao</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>data_hora_fim_inspecao</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>item conferido</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>quantidade refugada</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>codigo nc</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>observacao_refugo</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>observacao geral</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>item conferido</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>codigo nc</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>observacao_refugo</t>
         </is>
       </c>
     </row>
@@ -491,32 +513,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>deslizante</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>200</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>12/07/2026 16:48:00</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>12/07/2026 16:49:00</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Conforme</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Estator</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
         <is>
           <t>Item sem op</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -536,32 +572,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>pivotante</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>14/07/2026 14:36:00</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>14/07/2026 14:43:00</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Não conforme</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Estator</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
         <is>
           <t>Nao foi trocado a caixa de kit</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -581,32 +631,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>basculante</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>14/07/2026 15:40:00</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>14/07/2026 15:53:00</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Não conforme</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Estator</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
         <is>
           <t>Motor faltando parafuso</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -626,32 +690,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>pivotante</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>14/07/2026 16:00:00</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>14/07/2026 16:02:00</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Conforme</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Estator</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
         <is>
           <t>Capacitor de 30</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -671,33 +749,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>pivotante</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>14/07/2026 16:05:00</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>14/07/2026 16:12:00</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Não conforme</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Motores sujos de PU e óleo 
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Estator</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Motores sujos de PU e óleo 
 Etiqueta pivo na central pivo dupla</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -717,34 +809,48 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>pivotante</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>16/07/2026 15:20:00</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>16/07/2026 15:22:00</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Não conforme</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Motores sujos de PU
-Motor com 3 manuais 
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Estator</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Motores sujos de PU
+Motor com 3 manuais 
 Motor com etiquetas de pivô simples na central dupla</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -764,33 +870,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>pivotante</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>16/07/2026 15:23:00</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>16/07/2026 15:24:00</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Não conforme</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Parafuso do mancal solto 
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Estator</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Parafuso do mancal solto 
 Central 220v na linha de produção 127v</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -810,28 +930,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>pivotante</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>16/07/2026 15:25:00</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>16/07/2026 15:25:00</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Conforme</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Estator</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -851,28 +985,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>basculante</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>23/07/2026 07:35:00</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>23/07/2026 07:36:00</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Conforme</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Estator</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -890,30 +1038,40 @@
           <t>CONJ. MOVIMENTADOR INTELIGENTE - IZZY 300 220V 50-60HZ SEM CREMALHEIRA</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>29/07/2026 08:33:00</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>29/07/2026 08:37:00</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Conforme</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Estator</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -933,28 +1091,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>deslizante</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>29/07/2026 08:43:00</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>29/07/2026 08:46:00</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>Conforme</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Estator</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -974,28 +1146,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>deslizante</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>29/07/2026 08:43:00</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>29/07/2026 08:46:00</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Conforme</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Estator</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1015,28 +1201,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>deslizante</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>500</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>29/07/2026 08:47:00</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>29/07/2026 08:49:00</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Conforme</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Estator</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1056,28 +1256,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>deslizante</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>29/07/2026 08:49:00</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>29/07/2026 08:53:00</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Conforme</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Estator</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1097,28 +1311,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>pivotante</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>29/07/2026 08:56:00</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>29/07/2026 08:58:00</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Conforme</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Estator</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1138,32 +1366,46 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>pivotante</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>29/07/2026 08:58:00</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>29/07/2026 09:14:00</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Conforme</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Estator</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
         <is>
           <t>Kit flex na linha montando pivo duplo</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1183,32 +1425,46 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>pivotante</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>29/07/2026 09:15:00</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>29/07/2026 09:16:00</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Não conforme</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Estator</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
         <is>
           <t>Motores sujos de PU</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1228,28 +1484,42 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>basculante</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>29/07/2026 09:17:00</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>29/07/2026 09:18:00</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Conforme</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Estator</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1269,28 +1539,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>deslizante</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>03/08/2026 11:46:00</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>03/08/2026 11:48:00</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Estator</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1310,28 +1590,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>deslizante</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>03/08/2026 11:46:00</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>03/08/2026 11:48:00</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>Capacitor</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1351,28 +1641,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>basculante</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>03/08/2026 13:14:00</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>03/08/2026 13:19:00</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr">
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Estator</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
         <is>
           <t>INDUZIDO: Sem iduzido ate o momento da inspeção</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1392,29 +1696,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>pivotante</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>03/08/2026 13:23:00</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>03/08/2026 13:37:00</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>ETIQUETA INTERNA : Com op destinada a outro produto 
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Estator</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>ETIQUETA INTERNA : Com op destinada a outro produto 
 KIT : Sem kit ate o momento da inspeção</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1434,30 +1752,44 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>pivotante</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>03/08/2026 13:39:00</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>03/08/2026 13:48:00</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Sem kit para coNF
-PARAFUSO DA CARCAÇA : Faltando um parafuso
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Estator</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Sem kit para coNF
+PARAFUSO DA CARCAÇA : Faltando um parafuso
 LIMPEZA: sujo de PU</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1477,24 +1809,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>deslizante</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>03/08/2026 13:55:00</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>03/08/2026 14:00:00</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Estator</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1514,28 +1860,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>deslizante</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>03/08/2026 14:02:00</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>03/08/2026 14:17:00</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Estator</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
         <is>
           <t>Engrenagem montada errado</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1555,24 +1915,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>deslizante</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>03/08/2026 14:21:00</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>03/08/2026 14:25:00</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Estator</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1592,24 +1966,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>deslizante</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>03/08/2026 14:30:00</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>03/08/2026 14:31:00</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Estator</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1629,24 +2017,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t>basculante</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>04/08/2026 07:05:00</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>04/08/2026 07:08:00</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Estator</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1666,32 +2068,42 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t>pivotante</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>04/08/2026 07:20:00</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>04/08/2026 07:31:00</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Carcaça</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
         <is>
           <t>Carcaças trincadas</t>
         </is>
       </c>
+      <c r="M30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1711,32 +2123,42 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t>pivotante</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>04/08/2026 07:36:00</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>04/08/2026 07:44:00</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Carcaça</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
         <is>
           <t>Carcaças trincadas</t>
         </is>
       </c>
+      <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1756,32 +2178,42 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t>pivotante</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>04/08/2026 07:36:00</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>04/08/2026 07:44:00</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>Limpeza</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
         <is>
           <t>Motores sujos de PU</t>
         </is>
       </c>
+      <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1801,28 +2233,42 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t>deslizante</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>500</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>04/08/2026 08:16:00</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>04/08/2026 08:20:00</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr">
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Estator</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
         <is>
           <t>Pedido não tem etiqueta externa</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1842,24 +2288,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t>deslizante</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>04/08/2026 08:25:00</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>04/08/2026 08:28:00</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Estator</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1879,24 +2339,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t>deslizante</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>04/08/2026 08:39:00</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>04/08/2026 08:40:00</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Estator</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1916,24 +2390,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t>deslizante</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>04/08/2026 08:42:00</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>04/08/2026 08:45:00</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Estator</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1953,24 +2441,259 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t>basculante</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>04/08/2026 09:36:00</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>04/08/2026 09:38:00</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Estator</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>99174</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2008004</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CONJ. MOVIMENTADOR TRINO BV4 220V SEM ACIONAMENTO</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>basculante</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>04/08/2026 14:45:00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>04/08/2026 14:49:00</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Estator</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>98587</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2007089</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CONJUNTO MOVIMENTADOR TRINO PIVÔ 3 220V SEM ACIONAMENTO - DUPLO</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>pivotante</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>04/08/2026 14:51:00</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>04/08/2026 14:58:00</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Estator</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Sem kit</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>98421</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2007089</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CONJUNTO MOVIMENTADOR TRINO PIVÔ 3 220V SEM ACIONAMENTO - DUPLO</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>pivotante</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>04/08/2026 15:04:00</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>04/08/2026 16:00:00</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Etiqueta Externa</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Etiqueta externa com OP diferente da interna (OP de outro pedido)</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Sem kit 
+Motor sujo de PU</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>99197</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2006063</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CONJ. MOVIMENTADOR INTELIGENTE - IZZY 900 220V 50-60HZ SEM CREMALHEIRA</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>deslizante</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>06/08/2026 22:37:00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>06/08/2026 22:38:00</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Etiqueta Externa</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>trocada</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
